--- a/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>74.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>78</v>
       </c>
       <c r="U46" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -45220,7 +45220,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>80</v>
       </c>
       <c r="U163" t="n">
-        <v>12</v>
+        <v>10.1</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -46650,7 +46650,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>74.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -46739,12 +46739,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>35.4</v>
       </c>
       <c r="R2" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>54.8</v>
       </c>
       <c r="R3" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1656,7 +1656,7 @@
         <v>54.8</v>
       </c>
       <c r="R5" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>58.9</v>
+        <v>57.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>54.8</v>
       </c>
       <c r="R6" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>57.7</v>
+        <v>56.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>54.8</v>
       </c>
       <c r="R7" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2711,27 +2711,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,26 +2774,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.7</v>
+        <v>50.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S9" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2849,127 +2849,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8281</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3928</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2995,24 +2995,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,26 +3058,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.4</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.5</v>
+        <v>50.8</v>
       </c>
       <c r="R10" t="n">
         <v>56.7</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>70.59999999999999</v>
+        <v>7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3133,127 +3133,127 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.0984</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3279,27 +3279,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3309,26 +3309,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3342,61 +3342,57 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.2</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R11" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3413,12 +3409,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3428,112 +3424,112 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>100.2971</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.2071</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3548,7 +3544,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3559,27 +3555,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3589,17 +3585,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3626,22 +3622,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R12" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3655,7 +3651,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3675,7 +3671,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -3697,27 +3693,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3727,112 +3723,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.0984</t>
+          <t>100.8281</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.3928</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3843,24 +3839,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -3873,17 +3869,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3892,7 +3888,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3906,37 +3902,45 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.8</v>
+        <v>13.5</v>
       </c>
       <c r="R13" t="n">
         <v>56.7</v>
       </c>
       <c r="S13" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>44.5</v>
+        <v>56.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -3951,12 +3955,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3973,127 +3977,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.2971</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2071</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4119,27 +4123,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4149,26 +4153,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4182,26 +4186,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>50.1</v>
+        <v>36.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S14" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4210,34 +4214,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4257,27 +4257,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4287,112 +4287,112 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>54.8</v>
       </c>
       <c r="R15" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4687,27 +4687,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4717,26 +4717,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>48.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4754,22 +4754,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R16" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S16" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4778,33 +4778,37 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4836,12 +4840,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4851,97 +4855,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4956,7 +4960,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4967,12 +4971,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4997,7 +5001,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5016,7 +5020,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5030,26 +5034,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5101,12 +5105,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5116,12 +5120,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5131,67 +5135,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5226,12 +5230,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5247,12 +5251,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5277,7 +5281,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5296,7 +5300,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,11 +5314,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>34.6</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="n">
         <v>50.8</v>
@@ -5323,13 +5327,13 @@
         <v>56.7</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5363,12 +5367,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5385,12 +5389,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5400,12 +5404,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5415,67 +5419,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.3512</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5531,27 +5535,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5566,17 +5570,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5598,13 +5602,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>42.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.8</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -5613,7 +5617,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5622,37 +5626,33 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5699,112 +5699,112 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.3512</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5815,27 +5815,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5878,26 +5878,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>36.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.8</v>
+        <v>50.8</v>
       </c>
       <c r="R20" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S20" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5983,97 +5983,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>97.0663</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3852</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6099,27 +6099,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6162,26 +6162,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13.6</v>
+        <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R21" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S21" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>28.9</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6267,112 +6267,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>97.0663</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3852</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6667,27 +6667,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6697,26 +6697,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>45.3</v>
+        <v>44.8</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6730,26 +6730,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>23.7</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.4</v>
+        <v>50.8</v>
       </c>
       <c r="R23" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S23" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T23" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6758,33 +6758,37 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6801,12 +6805,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6816,12 +6820,12 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6831,97 +6835,97 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.81</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>99.655</t>
+          <t>98.3737</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.3886</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3196</t>
+          <t>0.2574</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>73.36</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1367</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6947,27 +6951,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6977,26 +6981,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -7010,26 +7014,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.8</v>
+        <v>34.4</v>
       </c>
       <c r="R24" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S24" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U24" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -7038,37 +7042,33 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7115,112 +7115,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>98.3737</t>
+          <t>99.655</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.3886</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.2574</t>
+          <t>0.3196</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.36</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1367</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7231,27 +7231,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enrique Hernández</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7261,26 +7261,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7294,23 +7294,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R25" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S25" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T25" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -7322,30 +7322,34 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7365,12 +7369,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7380,12 +7384,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7395,97 +7399,97 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>99.5161</t>
+          <t>100.7005</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4088</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3152</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
@@ -7500,7 +7504,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7511,27 +7515,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7541,26 +7545,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7574,23 +7578,23 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>40.2</v>
+        <v>39.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R26" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -7602,34 +7606,30 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7679,112 +7679,112 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>100.7005</t>
+          <t>99.5161</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4088</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3152</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>42.9</v>
+        <v>41.5</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>35.4</v>
       </c>
       <c r="R27" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S27" t="n">
         <v>64.3</v>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>42.5</v>
+        <v>41.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>35.4</v>
       </c>
       <c r="R28" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8334,12 +8334,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>54.8</v>
       </c>
       <c r="R29" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S29" t="n">
         <v>52.4</v>
@@ -8618,12 +8618,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>54.8</v>
       </c>
       <c r="R30" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S30" t="n">
         <v>44.8</v>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>35.4</v>
       </c>
       <c r="R37" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>35.4</v>
       </c>
       <c r="R2" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -11468,12 +11468,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>54.8</v>
       </c>
       <c r="R3" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -11752,12 +11752,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -12106,11 +12106,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -12130,7 +12130,7 @@
         <v>54.8</v>
       </c>
       <c r="R5" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -12320,12 +12320,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12390,7 +12390,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>58.9</v>
+        <v>57.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>54.8</v>
       </c>
       <c r="R6" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>57.7</v>
+        <v>56.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>54.8</v>
       </c>
       <c r="R7" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -12880,12 +12880,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -13185,27 +13185,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13215,17 +13215,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13234,7 +13234,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13248,26 +13248,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.7</v>
+        <v>50.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S9" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -13323,127 +13323,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8281</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3928</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13469,24 +13469,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -13499,17 +13499,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13532,26 +13532,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.4</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.5</v>
+        <v>50.8</v>
       </c>
       <c r="R10" t="n">
         <v>56.7</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>70.59999999999999</v>
+        <v>7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -13585,12 +13585,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -13607,127 +13607,127 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.0984</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -13753,27 +13753,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13783,26 +13783,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13816,61 +13816,57 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.2</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R11" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -13887,12 +13883,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -13902,112 +13898,112 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>100.2971</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.2071</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -14022,7 +14018,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -14033,27 +14029,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -14063,17 +14059,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14100,22 +14096,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R12" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -14129,7 +14125,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -14149,7 +14145,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -14171,27 +14167,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -14201,112 +14197,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.0984</t>
+          <t>100.8281</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.3928</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -14317,24 +14313,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -14347,17 +14343,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14366,7 +14362,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14380,37 +14376,45 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.8</v>
+        <v>13.5</v>
       </c>
       <c r="R13" t="n">
         <v>56.7</v>
       </c>
       <c r="S13" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>44.5</v>
+        <v>56.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -14425,12 +14429,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -14447,127 +14451,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.2971</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2071</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -14593,27 +14597,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14623,26 +14627,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14656,26 +14660,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>50.1</v>
+        <v>36.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S14" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14684,34 +14688,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -14731,27 +14731,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -14761,112 +14761,112 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14926,7 +14926,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>54.8</v>
       </c>
       <c r="R15" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -15140,12 +15140,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15161,27 +15161,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -15191,26 +15191,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>48.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15228,22 +15228,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R16" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S16" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15252,33 +15252,37 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -15300,7 +15304,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -15310,12 +15314,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15325,97 +15329,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -15430,7 +15434,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -15441,12 +15445,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15471,7 +15475,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -15490,7 +15494,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15504,26 +15508,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -15537,7 +15541,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -15575,12 +15579,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -15590,12 +15594,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -15605,67 +15609,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -15700,12 +15704,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -15721,12 +15725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15751,7 +15755,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -15770,7 +15774,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15784,11 +15788,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>34.6</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="n">
         <v>50.8</v>
@@ -15797,13 +15801,13 @@
         <v>56.7</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -15817,7 +15821,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -15837,12 +15841,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -15859,12 +15863,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -15874,12 +15878,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15889,67 +15893,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.3512</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -16005,27 +16009,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -16040,17 +16044,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -16072,13 +16076,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>42.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.8</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -16087,7 +16091,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -16096,37 +16100,33 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -16143,12 +16143,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -16158,12 +16158,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -16173,112 +16173,112 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.3512</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -16289,27 +16289,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16352,26 +16352,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>36.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.8</v>
+        <v>50.8</v>
       </c>
       <c r="R20" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S20" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16442,12 +16442,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16457,97 +16457,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>97.0663</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3852</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16573,27 +16573,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -16603,17 +16603,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16636,26 +16636,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13.6</v>
+        <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R21" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S21" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>28.9</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16726,12 +16726,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16741,112 +16741,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>97.0663</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3852</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
